--- a/tests/Fixtures/files/test_import_valid.xlsx
+++ b/tests/Fixtures/files/test_import_valid.xlsx
@@ -451,7 +451,7 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>12345678901234</v>
+        <v>55566677788899</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -474,7 +474,7 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>98765432109876</v>
+        <v>99988877766655</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -497,7 +497,7 @@
         <v>17</v>
       </c>
       <c r="B4">
-        <v>11122233344455</v>
+        <v>44433322211100</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
